--- a/config/demo/forms/app/oral_cancer_assessment.xlsx
+++ b/config/demo/forms/app/oral_cancer_assessment.xlsx
@@ -403,7 +403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M112"/>
+  <dimension ref="A1:M113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="8" min="1" max="1"/>
@@ -599,29 +599,29 @@
       </c>
     </row>
     <row r="8" ht="34.5" customHeight="1" s="9">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>form_start_timestamp</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>once(if(${_id} != '', now(), ''))</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>form_sync_timestamp</t>
         </is>
@@ -2661,19 +2661,36 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="8" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>form_submit_timestamp</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>now()</t>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>form_submit_timestamp_iso</t>
+        </is>
+      </c>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>format-date-time(now(), '%Y-%m-%dT%H:%M:%S+05:30')</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>form_submit_timestamp_display</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>format-date-time(now(), '%e-%b-%Y %H:%M:%S')</t>
         </is>
       </c>
     </row>

--- a/config/demo/forms/app/oral_cancer_assessment.xlsx
+++ b/config/demo/forms/app/oral_cancer_assessment.xlsx
@@ -345,7 +345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N173"/>
+  <dimension ref="A1:N174"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="3" min="1" max="1"/>
@@ -495,17 +495,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>reporter_name</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Reporter Name</t>
+          <t>contact_age</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>../inputs/user/name</t>
+          <t>../inputs/contact/date_of_birth</t>
         </is>
       </c>
     </row>
@@ -517,17 +512,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>reporter_place</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Reporter Place</t>
+          <t>contact_sex</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>instance('user-contact-summary')/context/facility_name</t>
+          <t>../inputs/contact/sex</t>
         </is>
       </c>
     </row>
@@ -539,126 +529,141 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>reporter_name</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Reporter Name</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>${patient_name}</t>
+          <t>../inputs/user/name</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="4">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>oral_intro_page</t>
+          <t>reporter_place</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Oral Cancer Screening</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>Reporter Place</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>instance('user-contact-summary')/context/facility_name</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="4">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>oral_intro_note</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>You will now ask questions and if needed take 8 photos of the oral cavity.</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>21056-oral-cancer-screening.jpg</t>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>${patient_name}</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="4">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>oral_intro_page</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Oral Cancer Screening</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="4">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>inputs</t>
+          <t>oral_intro_note</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Patient &amp; Reporter Info</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>You will now ask questions and if needed take 8 photos of the oral cavity.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="4">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>oral_intro_page</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="4">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>source_id</t>
+          <t>inputs</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Patient &amp; Reporter Info</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="4">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>hidden</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>source</t>
         </is>
       </c>
     </row>
@@ -670,114 +675,84 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>source_id</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="4">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>user</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="4">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>hidden</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>name</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="4">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>hidden</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>reporter_name_note</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Filled by: ${reporter_name}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="4">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>user</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="4">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>_id</t>
+          <t>reporter_name_note</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Patient's Name</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Select the patient from your area</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>select-contact type-patient</t>
+          <t>Filled by: ${reporter_name}</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="4">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>patient_id</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Medic ID</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>contact</t>
         </is>
       </c>
     </row>
@@ -789,144 +764,134 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>_id</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Patient Name</t>
+          <t>Patient's Name</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Select the patient from your area</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>select-contact type-patient role-patient</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="4">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>patient_id</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Medic ID</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="4">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>select_one states</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Patient Name</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>hidden</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="4">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>select_one districts</t>
+          <t>hidden</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>District</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>filter = ${state}</t>
+          <t>date_of_birth</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>${contact_age}</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="4">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>hidden</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>inputs</t>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>${contact_sex}</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="4">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Participant details</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>contact</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="4">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one states</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Enter age in completed years</t>
+          <t>State</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -934,36 +899,41 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 120</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>Age must be between 0 and 120</t>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="4">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>select_one gender</t>
+          <t>select_one districts</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>District</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>filter = ${state}</t>
         </is>
       </c>
     </row>
@@ -975,7 +945,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>participant</t>
+          <t>inputs</t>
         </is>
       </c>
     </row>
@@ -1259,6 +1229,11 @@
           <t>You will now take 8 photos of the oral cavity to identify lesions.</t>
         </is>
       </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>21056-oral-cancer-screening.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="4">
       <c r="A44" s="3" t="inlineStr">
@@ -1334,7 +1309,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Photo 1 Suspicion</t>
+          <t>Photo 1 Health Worker Observation</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -1417,7 +1392,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Photo 2 Suspicion</t>
+          <t>Photo 2 Health Worker Observation</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -1500,7 +1475,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Photo 3 Suspicion</t>
+          <t>Photo 3 Health Worker Observation</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -1583,7 +1558,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Photo 4 Suspicion</t>
+          <t>Photo 4 Health Worker Observation</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -1666,7 +1641,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Photo 5 Suspicion</t>
+          <t>Photo 5 Health Worker Observation</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -1749,7 +1724,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Photo 6 Suspicion</t>
+          <t>Photo 6 Health Worker Observation</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -1832,7 +1807,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Photo 7 Suspicion</t>
+          <t>Photo 7 Health Worker Observation</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -1915,7 +1890,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Photo 8 Suspicion</t>
+          <t>Photo 8 Health Worker Observation</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -1961,7 +1936,7 @@
     <row r="78" ht="15" customHeight="1" s="4">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>select_one suspicion</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -1972,6 +1947,16 @@
       <c r="C78" s="3" t="inlineStr">
         <is>
           <t>Final AI Recommendation</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>if(${final_ai_suspicion} != '', ${final_ai_suspicion}, 'non_suspicious')</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1991,6 +1976,16 @@
           <t>Referral Decision</t>
         </is>
       </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Please tell the client to consult a dentist as soon as possible. Provide all necessary instructions to reach the dentist's facility.</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
           <t>${final_ai_suspicion} = 'suspicious' or ${final_ai_suspicion} = 'non_suspicious'</t>
@@ -2352,1150 +2347,1145 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>**Age:** ${age}</t>
+          <t>**Age:** ${calc_age_lbl}</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="4">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_age</t>
+          <t>calc_age_lbl</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>number(format-date(today(), '%Y')) - number(format-date(${date_of_birth}, '%Y'))</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="4">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_gender</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_age</t>
         </is>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="4">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>lbl_gender</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>**Gender:** ${calc_gender_lbl}</t>
+          <t>grp_lbl_gender</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" s="4">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>calc_gender_lbl</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${gender},'${gender}')</t>
+          <t>lbl_gender</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>**Gender:** ${calc_gender_lbl}</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="4">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_gender</t>
+          <t>calc_gender_lbl</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>${contact_sex}</t>
         </is>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="4">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_hh_q1</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_gender</t>
         </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="4">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>lbl_hh_q1</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>**1. Cigarette / Bidi:** ${calc_cigarette_lbl}</t>
+          <t>grp_lbl_hh_q1</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" s="4">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>calc_cigarette_lbl</t>
-        </is>
-      </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${cigarette_bidi},'${cigarette_bidi}')</t>
+          <t>lbl_hh_q1</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>**1. Cigarette / Bidi:** ${calc_cigarette_lbl}</t>
         </is>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1" s="4">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_hh_q1</t>
+          <t>calc_cigarette_lbl</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${cigarette_bidi},'${cigarette_bidi}')</t>
         </is>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1" s="4">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_hh_q2</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_hh_q1</t>
         </is>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1" s="4">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>lbl_hh_q2</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>**2. Smokeless Tobacco:** ${calc_smokeless_lbl}</t>
+          <t>grp_lbl_hh_q2</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" s="4">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>calc_smokeless_lbl</t>
-        </is>
-      </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${smokeless_tobacco},'${smokeless_tobacco}')</t>
+          <t>lbl_hh_q2</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>**2. Smokeless Tobacco:** ${calc_smokeless_lbl}</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" s="4">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_hh_q2</t>
+          <t>calc_smokeless_lbl</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${smokeless_tobacco},'${smokeless_tobacco}')</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="4">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_hh_q3</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_hh_q2</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="4">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>lbl_hh_q3</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>**3. Areca Nut:** ${calc_areca_lbl}</t>
+          <t>grp_lbl_hh_q3</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="4">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>calc_areca_lbl</t>
-        </is>
-      </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${areca_nut},'${areca_nut}')</t>
+          <t>lbl_hh_q3</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>**3. Areca Nut:** ${calc_areca_lbl}</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="4">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_hh_q3</t>
+          <t>calc_areca_lbl</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${areca_nut},'${areca_nut}')</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="4">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_hh_q4</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_hh_q3</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="4">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>lbl_hh_q4</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>**4. Alcohol:** ${calc_alcohol_lbl}</t>
+          <t>grp_lbl_hh_q4</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="4">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>calc_alcohol_lbl</t>
-        </is>
-      </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${alcohol},'${alcohol}')</t>
+          <t>lbl_hh_q4</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>**4. Alcohol:** ${calc_alcohol_lbl}</t>
         </is>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="4">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_hh_q4</t>
+          <t>calc_alcohol_lbl</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${alcohol},'${alcohol}')</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="4">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_hh_q5</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>${alcohol} = 'current'</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_hh_q4</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" s="4">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>lbl_hh_q5</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>**5. Alcohol Frequency (days/week):** ${alcohol_frequency}</t>
+          <t>grp_lbl_hh_q5</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>${alcohol} = 'current'</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="4">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_hh_q5</t>
+          <t>lbl_hh_q5</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>**5. Alcohol Frequency (days/week):** ${alcohol_frequency}</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="4">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_1</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t>${all_habits_never} = 'no'</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_hh_q5</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="4">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>lbl_photo_1_suspicion</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>**Photo 1 Suspicion:** ${calc_photo_1_suspicion_lbl}</t>
+          <t>grp_lbl_photo_1</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>${all_habits_never} = 'no'</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" s="4">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>calc_photo_1_suspicion_lbl</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${ai_photo_1_suspicion},'${ai_photo_1_suspicion}')</t>
+          <t>lbl_photo_1_suspicion</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>**Photo 1 Health Worker Observation:** ${calc_photo_1_suspicion_lbl}</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="4">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_1</t>
+          <t>calc_photo_1_suspicion_lbl</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${ai_photo_1_suspicion},'${ai_photo_1_suspicion}')</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="4">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_2</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t>${all_habits_never} = 'no'</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_photo_1</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="4">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>lbl_photo_2_suspicion</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>**Photo 2 Suspicion:** ${calc_photo_2_suspicion_lbl}</t>
+          <t>grp_lbl_photo_2</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>${all_habits_never} = 'no'</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="4">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>calc_photo_2_suspicion_lbl</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${ai_photo_2_suspicion},'${ai_photo_2_suspicion}')</t>
+          <t>lbl_photo_2_suspicion</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>**Photo 2 Health Worker Observation:** ${calc_photo_2_suspicion_lbl}</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="4">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_2</t>
+          <t>calc_photo_2_suspicion_lbl</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${ai_photo_2_suspicion},'${ai_photo_2_suspicion}')</t>
         </is>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1" s="4">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_3</t>
-        </is>
-      </c>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t>${all_habits_never} = 'no'</t>
-        </is>
-      </c>
-      <c r="G134" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_photo_2</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="4">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>lbl_photo_3_suspicion</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>**Photo 3 Suspicion:** ${calc_photo_3_suspicion_lbl}</t>
+          <t>grp_lbl_photo_3</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>${all_habits_never} = 'no'</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" s="4">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>calc_photo_3_suspicion_lbl</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${ai_photo_3_suspicion},'${ai_photo_3_suspicion}')</t>
+          <t>lbl_photo_3_suspicion</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>**Photo 3 Health Worker Observation:** ${calc_photo_3_suspicion_lbl}</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" s="4">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_3</t>
+          <t>calc_photo_3_suspicion_lbl</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${ai_photo_3_suspicion},'${ai_photo_3_suspicion}')</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" s="4">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_4</t>
-        </is>
-      </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t>${all_habits_never} = 'no'</t>
-        </is>
-      </c>
-      <c r="G138" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_photo_3</t>
         </is>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="4">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>lbl_photo_4_suspicion</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>**Photo 4 Suspicion:** ${calc_photo_4_suspicion_lbl}</t>
+          <t>grp_lbl_photo_4</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>${all_habits_never} = 'no'</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" s="4">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>calc_photo_4_suspicion_lbl</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${ai_photo_4_suspicion},'${ai_photo_4_suspicion}')</t>
+          <t>lbl_photo_4_suspicion</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>**Photo 4 Health Worker Observation:** ${calc_photo_4_suspicion_lbl}</t>
         </is>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" s="4">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_4</t>
+          <t>calc_photo_4_suspicion_lbl</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${ai_photo_4_suspicion},'${ai_photo_4_suspicion}')</t>
         </is>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="4">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_5</t>
-        </is>
-      </c>
-      <c r="F142" s="3" t="inlineStr">
-        <is>
-          <t>${all_habits_never} = 'no'</t>
-        </is>
-      </c>
-      <c r="G142" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_photo_4</t>
         </is>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="4">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>lbl_photo_5_suspicion</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>**Photo 5 Suspicion:** ${calc_photo_5_suspicion_lbl}</t>
+          <t>grp_lbl_photo_5</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>${all_habits_never} = 'no'</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1" s="4">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>calc_photo_5_suspicion_lbl</t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${ai_photo_5_suspicion},'${ai_photo_5_suspicion}')</t>
+          <t>lbl_photo_5_suspicion</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>**Photo 5 Health Worker Observation:** ${calc_photo_5_suspicion_lbl}</t>
         </is>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" s="4">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_5</t>
+          <t>calc_photo_5_suspicion_lbl</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${ai_photo_5_suspicion},'${ai_photo_5_suspicion}')</t>
         </is>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1" s="4">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_6</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>${all_habits_never} = 'no'</t>
-        </is>
-      </c>
-      <c r="G146" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_photo_5</t>
         </is>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1" s="4">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>lbl_photo_6_suspicion</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>**Photo 6 Suspicion:** ${calc_photo_6_suspicion_lbl}</t>
+          <t>grp_lbl_photo_6</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>${all_habits_never} = 'no'</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1" s="4">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>calc_photo_6_suspicion_lbl</t>
-        </is>
-      </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${ai_photo_6_suspicion},'${ai_photo_6_suspicion}')</t>
+          <t>lbl_photo_6_suspicion</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>**Photo 6 Health Worker Observation:** ${calc_photo_6_suspicion_lbl}</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="4">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_6</t>
+          <t>calc_photo_6_suspicion_lbl</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${ai_photo_6_suspicion},'${ai_photo_6_suspicion}')</t>
         </is>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1" s="4">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_7</t>
-        </is>
-      </c>
-      <c r="F150" s="3" t="inlineStr">
-        <is>
-          <t>${all_habits_never} = 'no'</t>
-        </is>
-      </c>
-      <c r="G150" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_photo_6</t>
         </is>
       </c>
     </row>
     <row r="151" ht="15" customHeight="1" s="4">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>lbl_photo_7_suspicion</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>**Photo 7 Suspicion:** ${calc_photo_7_suspicion_lbl}</t>
+          <t>grp_lbl_photo_7</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>${all_habits_never} = 'no'</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="152" ht="15" customHeight="1" s="4">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>calc_photo_7_suspicion_lbl</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${ai_photo_7_suspicion},'${ai_photo_7_suspicion}')</t>
+          <t>lbl_photo_7_suspicion</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>**Photo 7 Health Worker Observation:** ${calc_photo_7_suspicion_lbl}</t>
         </is>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1" s="4">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_7</t>
+          <t>calc_photo_7_suspicion_lbl</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${ai_photo_7_suspicion},'${ai_photo_7_suspicion}')</t>
         </is>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1" s="4">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_8</t>
-        </is>
-      </c>
-      <c r="F154" s="3" t="inlineStr">
-        <is>
-          <t>${all_habits_never} = 'no'</t>
-        </is>
-      </c>
-      <c r="G154" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_photo_7</t>
         </is>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1" s="4">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>lbl_photo_8_suspicion</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>**Photo 8 Suspicion:** ${calc_photo_8_suspicion_lbl}</t>
+          <t>grp_lbl_photo_8</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>${all_habits_never} = 'no'</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1" s="4">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>calc_photo_8_suspicion_lbl</t>
-        </is>
-      </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${ai_photo_8_suspicion},'${ai_photo_8_suspicion}')</t>
+          <t>lbl_photo_8_suspicion</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>**Photo 8 Health Worker Observation:** ${calc_photo_8_suspicion_lbl}</t>
         </is>
       </c>
     </row>
     <row r="157" ht="15" customHeight="1" s="4">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_photo_8</t>
+          <t>calc_photo_8_suspicion_lbl</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${ai_photo_8_suspicion},'${ai_photo_8_suspicion}')</t>
         </is>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1" s="4">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_final_suspicion</t>
-        </is>
-      </c>
-      <c r="F158" s="3" t="inlineStr">
-        <is>
-          <t>${all_habits_never} = 'no'</t>
-        </is>
-      </c>
-      <c r="G158" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_photo_8</t>
         </is>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1" s="4">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>lbl_final_suspicion</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="inlineStr">
-        <is>
-          <t>**Final AI Recommendation:** ${calc_final_suspicion_lbl}</t>
+          <t>grp_lbl_final_suspicion</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>${all_habits_never} = 'no'</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1" s="4">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>calc_final_suspicion_lbl</t>
-        </is>
-      </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${final_ai_suspicion},'${final_ai_suspicion}')</t>
+          <t>lbl_final_suspicion</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>**Final AI Recommendation:** ${calc_final_suspicion_lbl}</t>
         </is>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1" s="4">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_final_suspicion</t>
+          <t>calc_final_suspicion_lbl</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>${final_ai_suspicion}</t>
         </is>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1" s="4">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_final_referral</t>
-        </is>
-      </c>
-      <c r="F162" s="3" t="inlineStr">
-        <is>
-          <t>${all_habits_never} = 'no' and (${final_ai_suspicion} = 'non_suspicious' or ${final_ai_suspicion} = 'suspicious')</t>
-        </is>
-      </c>
-      <c r="G162" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_final_suspicion</t>
         </is>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1" s="4">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>lbl_final_referral</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>**Referral Decision:** ${calc_final_referral_lbl}</t>
+          <t>grp_lbl_final_referral</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>${all_habits_never} = 'no' and (${final_ai_suspicion} = 'non_suspicious' or ${final_ai_suspicion} = 'suspicious')</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1" s="4">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>calc_final_referral_lbl</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>jr:choice-name(${final_ai_referral},'${final_ai_referral}')</t>
+          <t>lbl_final_referral</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>**Referral Decision:** ${calc_final_referral_lbl}</t>
         </is>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1" s="4">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_final_referral</t>
+          <t>calc_final_referral_lbl</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>jr:choice-name(${final_ai_referral},'${final_ai_referral}')</t>
         </is>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1" s="4">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_habit_status</t>
-        </is>
-      </c>
-      <c r="G166" s="3" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>grp_lbl_final_referral</t>
         </is>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1" s="4">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>lbl_habit_status</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>**Habit Status:** ${calc_habit_status_lbl}</t>
+          <t>grp_lbl_habit_status</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="168" ht="15" customHeight="1" s="4">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>calc_habit_status_lbl</t>
-        </is>
-      </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>if(${all_habits_never} = 'yes','As per Habit History, nothing suspicious is found. So no need of Oral Visual Examination ','Patient has habit history. Photos are captured for Oral Exam.')</t>
+          <t>lbl_habit_status</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>**Habit Status:** ${calc_habit_status_lbl}</t>
         </is>
       </c>
     </row>
     <row r="169" ht="15" customHeight="1" s="4">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>grp_lbl_habit_status</t>
+          <t>calc_habit_status_lbl</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>if(${all_habits_never} = 'yes','As per Habit History, nothing suspicious is found. So no need of Oral Visual Examination ','Patient has habit history. Photos are captured for Oral Exam.')</t>
         </is>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1" s="4">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>ai_analysis_summary</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="G170" s="3" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>grp_lbl_habit_status</t>
         </is>
       </c>
     </row>
@@ -3507,17 +3497,17 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>ai_analysis_status</t>
+          <t>ai_analysis_summary</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Analysis Status</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>multiline hidden</t>
         </is>
       </c>
     </row>
@@ -3529,12 +3519,12 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>ai_analysis_error</t>
+          <t>ai_analysis_status</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Error (if any)</t>
+          <t>Analysis Status</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -3546,15 +3536,40 @@
     <row r="173" ht="15" customHeight="1" s="4">
       <c r="A173" s="3" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>ai_analysis_error</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Error (if any)</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="15" customHeight="1" s="4">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
           <t>end_group</t>
         </is>
       </c>
-      <c r="B173" s="3" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t>group_summary</t>
         </is>
       </c>
     </row>
+    <row r="1048574" ht="12.8" customHeight="1" s="4"/>
+    <row r="1048575" ht="12.8" customHeight="1" s="4"/>
+    <row r="1048576" ht="12.8" customHeight="1" s="4"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
